--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486474_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486474_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7237</v>
+        <v>1.1876</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6246</v>
+        <v>4.947</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.901</v>
+        <v>-3.7594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3778</v>
+        <v>4.8565</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7906</v>
+        <v>0.4196</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4128</v>
+        <v>4.4369</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4586</v>
+        <v>8.417199999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7884</v>
+        <v>2.4303</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6702</v>
+        <v>5.9868</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0808</v>
+        <v>-3.5606</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9978</v>
+        <v>-2.0107</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0829</v>
+        <v>-1.5499</v>
       </c>
       <c r="P2" t="n">
-        <v>0.435</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2175</v>
+        <v>-4.5676</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0892</v>
+        <v>-0.7108</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6165</v>
+        <v>-0.0324</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5273</v>
+        <v>-0.6784</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6486</v>
+        <v>0.7143</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1928</v>
+        <v>1.9851</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.5442</v>
+        <v>-1.2708</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.02</v>
+        <v>0.3778</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.3968</v>
+        <v>0.7906</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6232</v>
+        <v>-0.4128</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3886</v>
+        <v>2.4586</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0793</v>
+        <v>1.7884</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3092</v>
+        <v>0.6702</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.4086</v>
+        <v>-2.0808</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4762</v>
+        <v>-0.9978</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9324</v>
+        <v>-1.0829</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.0985</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3942</v>
+        <v>-0.256</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9542</v>
+        <v>0.1574</v>
       </c>
       <c r="V3" t="n">
-        <v>5.2286</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>4.7151</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6102</v>
+        <v>0.3696</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6203</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0101</v>
+        <v>-0.1642</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5116000000000001</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0342</v>
+        <v>-0.2064</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971</v>
+        <v>0.1106</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1628</v>
+        <v>-0.317</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2551</v>
+        <v>0.3638</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9360000000000001</v>
+        <v>3.908</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-3.5442</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6818</v>
+        <v>-4.02</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3375</v>
+        <v>-2.3968</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3442</v>
+        <v>-1.6232</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1327</v>
+        <v>0.3886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0944</v>
+        <v>0.0793</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0382</v>
+        <v>0.3092</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8144</v>
+        <v>-4.4086</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.432</v>
+        <v>-2.4762</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3825</v>
+        <v>-1.9324</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7193000000000001</v>
+        <v>-0.8448</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6081</v>
+        <v>0.1094</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1113</v>
+        <v>-0.9542</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.2286</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>4.7151</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2269</v>
+        <v>-0.135</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2945</v>
+        <v>0.6692</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.0677</v>
+        <v>-0.8042</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8565</v>
+        <v>-0.6818</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4196</v>
+        <v>-0.3375</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4369</v>
+        <v>-0.3442</v>
       </c>
       <c r="J6" t="n">
-        <v>8.417199999999999</v>
+        <v>0.1327</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4303</v>
+        <v>0.0944</v>
       </c>
       <c r="L6" t="n">
-        <v>5.9868</v>
+        <v>0.0382</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5606</v>
+        <v>-0.8144</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0107</v>
+        <v>-0.432</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5499</v>
+        <v>-0.3825</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6976</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5676</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6716</v>
+        <v>0.3293</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.3413</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9866</v>
+        <v>-0.012</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3904</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.9201</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.584</v>
+        <v>-0.7823</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.107</v>
+        <v>-0.1378</v>
       </c>
       <c r="G7" t="n">
         <v>-1.335</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.2376</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2656</v>
+        <v>0.0673</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2741</v>
+        <v>-0.3049</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4369</v>
+        <v>-1.9531</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5777</v>
+        <v>-1.2172</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8592</v>
+        <v>-0.7359</v>
       </c>
       <c r="G8" t="n">
         <v>0.8425</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0618</v>
+        <v>-0.578</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.548</v>
+        <v>-0.1875</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5138</v>
+        <v>-0.3906</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7904</v>
+        <v>-2.3057</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.057</v>
+        <v>0.4586</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7334</v>
+        <v>-2.7642</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2613</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6166</v>
+        <v>-0.1319</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>0.173</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2741</v>
+        <v>-0.3049</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>J. BONE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1048</v>
+        <v>-3.4245</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6989</v>
+        <v>1.2912</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4058</v>
+        <v>-4.7158</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2567</v>
+        <v>-1.5784</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2861</v>
+        <v>-0.8549</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9706</v>
+        <v>-0.7235</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0926</v>
+        <v>2.5808</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8942</v>
+        <v>1.3719</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8016</v>
+        <v>1.2089</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3493</v>
+        <v>-4.1591</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1803</v>
+        <v>-2.2267</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1689</v>
+        <v>-1.9324</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3171</v>
+        <v>-1.4027</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.3749</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7006</v>
+        <v>-1.0278</v>
       </c>
       <c r="V10" t="n">
         <v>-0.226</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.226</v>
+        <v>-0.6163999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BONE</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4915</v>
+        <v>-3.701</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5017</v>
+        <v>-2.2952</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9932</v>
+        <v>-1.4058</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5784</v>
+        <v>-1.2567</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8549</v>
+        <v>-0.2861</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7235</v>
+        <v>-0.9706</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5808</v>
+        <v>0.0926</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3719</v>
+        <v>0.8942</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2089</v>
+        <v>-0.8016</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.1591</v>
+        <v>-1.3493</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2267</v>
+        <v>-1.1803</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9324</v>
+        <v>-0.1689</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4696</v>
+        <v>-0.9133</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1644</v>
+        <v>-0.2127</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3052</v>
+        <v>-0.7006</v>
       </c>
       <c r="V11" t="n">
         <v>-0.226</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.843</v>
+        <v>-4.6172</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0725</v>
+        <v>-1.2989</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7705</v>
+        <v>-3.3183</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5164</v>
+        <v>-3.7579</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8008</v>
+        <v>-1.2351</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7156</v>
+        <v>-2.5228</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6722</v>
+        <v>-1.9927</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1095</v>
+        <v>0.1277</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7817</v>
+        <v>-2.1204</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8442</v>
+        <v>-1.7652</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9103</v>
+        <v>-1.3628</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9339</v>
+        <v>-0.4024</v>
       </c>
       <c r="P12" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1593</v>
+        <v>-1.7208</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5997</v>
+        <v>-0.4362</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4403</v>
+        <v>-1.2846</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.921</v>
+        <v>-0.226</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.921</v>
+        <v>-1.356</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0577</v>
+        <v>-5.4746</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6162</v>
+        <v>-0.5809</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.4416</v>
+        <v>-4.8938</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.7579</v>
+        <v>-3.5164</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2351</v>
+        <v>-1.8008</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5228</v>
+        <v>-1.7156</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9927</v>
+        <v>-0.6722</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1277</v>
+        <v>0.1095</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1204</v>
+        <v>-0.7817</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7652</v>
+        <v>-2.8442</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3628</v>
+        <v>-1.9103</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4024</v>
+        <v>-0.9339</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1614</v>
+        <v>-0.4723</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4079</v>
+        <v>-0.5636</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.226</v>
+        <v>-1.921</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.356</v>
+        <v>-1.921</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.9508</v>
+        <v>-19.8959</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5636</v>
+        <v>7.618399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-27.5146</v>
+        <v>-27.5144</v>
       </c>
       <c r="G14" t="n">
         <v>-11.8423</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.893999999999999</v>
+        <v>-7.894</v>
       </c>
       <c r="I14" t="n">
         <v>-3.948300000000001</v>
@@ -1522,10 +1522,10 @@
         <v>12.6275</v>
       </c>
       <c r="K14" t="n">
-        <v>6.068799999999999</v>
+        <v>6.0688</v>
       </c>
       <c r="L14" t="n">
-        <v>6.558299999999999</v>
+        <v>6.5583</v>
       </c>
       <c r="M14" t="n">
         <v>-24.4696</v>
@@ -1537,22 +1537,22 @@
         <v>-10.5065</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.175099999999999</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.9628</v>
       </c>
       <c r="R14" t="n">
-        <v>9.787500000000001</v>
+        <v>9.7875</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.042999999999999</v>
+        <v>-6.987800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.6617</v>
+        <v>-0.6067999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.380999999999999</v>
+        <v>-6.381200000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.1091</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3755</v>
+        <v>5.9218</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1742</v>
+        <v>4.1787</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2013</v>
+        <v>1.7431</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2302</v>
+        <v>2.398</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8708</v>
+        <v>2.1382</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3594</v>
+        <v>0.2598</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2399</v>
+        <v>2.3057</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4367</v>
+        <v>3.0691</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8032</v>
+        <v>-0.7634</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0097</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5659</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5562</v>
+        <v>1.0231</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1448</v>
+        <v>1.0464</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7613</v>
+        <v>0.7006</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3835</v>
+        <v>0.3458</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8695</v>
+        <v>2.2599</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7395</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2277</v>
+        <v>5.1352</v>
       </c>
       <c r="E16" t="n">
         <v>2.7307</v>
       </c>
       <c r="F16" t="n">
-        <v>2.497</v>
+        <v>2.4046</v>
       </c>
       <c r="G16" t="n">
         <v>3.5994</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9334</v>
+        <v>0.8409</v>
       </c>
       <c r="T16" t="n">
         <v>0.5516</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3818</v>
+        <v>0.2893</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.9969</v>
+        <v>4.7249</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2846</v>
+        <v>1.9621</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7123</v>
+        <v>2.7628</v>
       </c>
       <c r="G17" t="n">
-        <v>2.398</v>
+        <v>2.6311</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1382</v>
+        <v>1.9282</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2598</v>
+        <v>0.7028</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3057</v>
+        <v>3.0208</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0691</v>
+        <v>2.4272</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7634</v>
+        <v>0.5937</v>
       </c>
       <c r="M17" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.3898</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.4989</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0231</v>
+        <v>0.1091</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1215</v>
+        <v>1.5718</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1935</v>
+        <v>1.1164</v>
       </c>
       <c r="U17" t="n">
-        <v>0.315</v>
+        <v>0.4554</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2599</v>
+        <v>0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2663</v>
+        <v>4.6182</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6269</v>
+        <v>3.386</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6395</v>
+        <v>1.2322</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6311</v>
+        <v>3.2302</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9282</v>
+        <v>1.8708</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7028</v>
+        <v>1.3594</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0208</v>
+        <v>3.2399</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4272</v>
+        <v>2.4367</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5937</v>
+        <v>0.8032</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3898</v>
+        <v>-0.0097</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4989</v>
+        <v>-0.5659</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1091</v>
+        <v>0.5562</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1133</v>
+        <v>2.3875</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7811</v>
+        <v>1.9732</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3321</v>
+        <v>0.4143</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7395</v>
+        <v>-1.8695</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4094</v>
+        <v>2.9181</v>
       </c>
       <c r="E19" t="n">
-        <v>6.075</v>
+        <v>6.5221</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6656</v>
+        <v>-3.604</v>
       </c>
       <c r="G19" t="n">
         <v>1.8306</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2689</v>
+        <v>0.2397</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3305</v>
+        <v>0.1166</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0615</v>
+        <v>0.1232</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7088</v>
+        <v>1.5354</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3052</v>
+        <v>3.1934</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5964</v>
+        <v>-1.6581</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7226</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3014</v>
+        <v>0.128</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1971</v>
+        <v>0.0853</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1043</v>
+        <v>0.0427</v>
       </c>
       <c r="V20" t="n">
         <v>1.695</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3058</v>
+        <v>0.9204</v>
       </c>
       <c r="E21" t="n">
-        <v>0.231</v>
+        <v>-0.216</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0748</v>
+        <v>1.1365</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8594000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3822</v>
+        <v>0.9968</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3087</v>
+        <v>0.8616</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0735</v>
+        <v>0.1352</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7395</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7728</v>
+        <v>0.6495</v>
       </c>
       <c r="E22" t="n">
         <v>0.3285</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4443</v>
+        <v>0.321</v>
       </c>
       <c r="G22" t="n">
         <v>0.295</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2603</v>
+        <v>0.137</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2603</v>
+        <v>0.137</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3087</v>
+        <v>-0.2162</v>
       </c>
       <c r="E23" t="n">
         <v>5.0966</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4053</v>
+        <v>-5.3128</v>
       </c>
       <c r="G23" t="n">
         <v>1.9423</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5087</v>
+        <v>0.6011</v>
       </c>
       <c r="T23" t="n">
         <v>0.4951</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0136</v>
+        <v>0.106</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1947</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.435</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5483</v>
+        <v>1.3248</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9833</v>
+        <v>-2.1066</v>
       </c>
       <c r="G24" t="n">
         <v>-0.077</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4898</v>
+        <v>0.143</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1971</v>
+        <v>-0.0264</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2927</v>
+        <v>0.1694</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1952</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3688</v>
+        <v>-3.4747</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8866</v>
+        <v>-0.9925</v>
       </c>
       <c r="F25" t="n">
         <v>-2.4822</v>
@@ -2404,10 +2404,10 @@
         <v>1.305</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0565</v>
+        <v>0.9505</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3869</v>
+        <v>0.5071</v>
       </c>
       <c r="U25" t="n">
         <v>0.4434</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>21.9507</v>
+        <v>21.9508</v>
       </c>
       <c r="E26" t="n">
         <v>27.5144</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.563600000000001</v>
+        <v>-5.563499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>11.8423</v>
@@ -2482,10 +2482,10 @@
         <v>11.9628</v>
       </c>
       <c r="S26" t="n">
-        <v>9.042999999999999</v>
+        <v>9.0427</v>
       </c>
       <c r="T26" t="n">
-        <v>6.3811</v>
+        <v>6.381100000000001</v>
       </c>
       <c r="U26" t="n">
         <v>2.6617</v>
